--- a/artfynd/A 17959-2026 artfynd.xlsx
+++ b/artfynd/A 17959-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>108851246</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551272.6189296143</v>
+        <v>551272</v>
       </c>
       <c r="R2" t="n">
-        <v>6331123.279908659</v>
+        <v>6331123</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108851061</v>
+        <v>108851250</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,43 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjösebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551241.7503164235</v>
+        <v>551260</v>
       </c>
       <c r="R3" t="n">
-        <v>6331112.038396452</v>
+        <v>6331139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,6 +860,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,6 +876,218 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108850982</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mjösebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>551241</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6331130</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108851061</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mjösebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>551241</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6331112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Viktor Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17959-2026 artfynd.xlsx
+++ b/artfynd/A 17959-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851246</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108850982</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,8 +1108,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>